--- a/refs/heads/main/StructureDefinition-ServiceRequestRevisarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-ServiceRequestRevisarLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="560">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1098,7 +1098,7 @@
     <t>ServiceRequest.priority</t>
   </si>
   <si>
-    <t>Prioridad Recomendada Interconsulta de Origen</t>
+    <t>Pertinencia Interconsulta</t>
   </si>
   <si>
     <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
@@ -1161,14 +1161,11 @@
     <t>ServiceRequest.doNotPerform.extension</t>
   </si>
   <si>
-    <t>MotivoNoPertinenciaCodigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MotivoNoPertinenciaLE}
+    <t>PertinenciaInterconsulta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertinenciaInterconsulta}
 </t>
-  </si>
-  <si>
-    <t>Motivo No Pertinencia</t>
   </si>
   <si>
     <t>ServiceRequest.doNotPerform.value</t>
@@ -2070,7 +2067,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.2734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.34375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.4140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -6227,7 +6224,7 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>84</v>
@@ -7047,10 +7044,10 @@
         <v>372</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -7133,7 +7130,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7159,10 +7156,10 @@
         <v>333</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -7213,7 +7210,7 @@
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>75</v>
@@ -7245,11 +7242,11 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7271,13 +7268,13 @@
         <v>179</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7306,11 +7303,11 @@
         <v>284</v>
       </c>
       <c r="X46" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Y46" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Y46" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="Z46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7327,7 +7324,7 @@
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>75</v>
@@ -7342,28 +7339,28 @@
         <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AK46" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AK46" t="s" s="2">
+      <c r="AL46" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7385,13 +7382,13 @@
         <v>179</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -7420,11 +7417,11 @@
         <v>284</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Y47" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="Z47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7441,7 +7438,7 @@
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>75</v>
@@ -7450,7 +7447,7 @@
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>96</v>
@@ -7459,21 +7456,21 @@
         <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7496,17 +7493,17 @@
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>77</v>
@@ -7555,7 +7552,7 @@
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>75</v>
@@ -7573,10 +7570,10 @@
         <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7587,7 +7584,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7610,13 +7607,13 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="K49" t="s" s="2">
+      <c r="L49" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -7667,7 +7664,7 @@
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>84</v>
@@ -7682,28 +7679,28 @@
         <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AK49" t="s" s="2">
+      <c r="AL49" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7722,13 +7719,13 @@
         <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="K50" t="s" s="2">
+      <c r="L50" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -7779,7 +7776,7 @@
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>75</v>
@@ -7794,28 +7791,28 @@
         <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AK50" t="s" s="2">
+      <c r="AL50" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7834,13 +7831,13 @@
         <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="K51" t="s" s="2">
+      <c r="L51" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7891,7 +7888,7 @@
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>75</v>
@@ -7906,24 +7903,24 @@
         <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AK51" t="s" s="2">
+      <c r="AL51" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7946,13 +7943,13 @@
         <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="K52" t="s" s="2">
+      <c r="L52" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7982,11 +7979,11 @@
         <v>284</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="Z52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8003,7 +8000,7 @@
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
@@ -8024,22 +8021,22 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>441</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8058,13 +8055,13 @@
         <v>85</v>
       </c>
       <c r="J53" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="K53" t="s" s="2">
+      <c r="L53" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -8115,7 +8112,7 @@
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
@@ -8130,28 +8127,28 @@
         <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AK53" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AK53" t="s" s="2">
+      <c r="AL53" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8170,16 +8167,16 @@
         <v>85</v>
       </c>
       <c r="J54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="K54" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="K54" t="s" s="2">
+      <c r="L54" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -8229,7 +8226,7 @@
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -8244,28 +8241,28 @@
         <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AK54" t="s" s="2">
+      <c r="AL54" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8287,13 +8284,13 @@
         <v>179</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
@@ -8322,11 +8319,11 @@
         <v>284</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="Y55" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="Z55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8343,7 +8340,7 @@
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>75</v>
@@ -8358,16 +8355,16 @@
         <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AK55" t="s" s="2">
+      <c r="AL55" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8375,11 +8372,11 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8398,16 +8395,16 @@
         <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="K56" t="s" s="2">
+      <c r="L56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8457,7 +8454,7 @@
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>75</v>
@@ -8472,16 +8469,16 @@
         <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK56" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AK56" t="s" s="2">
+      <c r="AL56" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8489,7 +8486,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8515,10 +8512,10 @@
         <v>179</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8548,11 +8545,11 @@
         <v>284</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="Y57" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="Z57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8569,7 +8566,7 @@
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
@@ -8590,10 +8587,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8601,7 +8598,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8624,13 +8621,13 @@
         <v>85</v>
       </c>
       <c r="J58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8681,7 +8678,7 @@
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>75</v>
@@ -8702,10 +8699,10 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8713,7 +8710,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8739,13 +8736,13 @@
         <v>179</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -8774,11 +8771,11 @@
         <v>284</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="Y59" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="Z59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8795,7 +8792,7 @@
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
@@ -8810,16 +8807,16 @@
         <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AK59" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AK59" t="s" s="2">
+      <c r="AL59" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8827,7 +8824,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8850,16 +8847,16 @@
         <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="K60" t="s" s="2">
+      <c r="L60" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
@@ -8909,7 +8906,7 @@
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
@@ -8924,16 +8921,16 @@
         <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK60" t="s" s="2">
+      <c r="AL60" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AM60" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8941,7 +8938,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8964,13 +8961,13 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="K61" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="K61" t="s" s="2">
+      <c r="L61" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -9021,7 +9018,7 @@
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>75</v>
@@ -9036,13 +9033,13 @@
         <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9053,11 +9050,11 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9076,16 +9073,16 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="K62" t="s" s="2">
+      <c r="L62" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
@@ -9135,7 +9132,7 @@
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>75</v>
@@ -9150,13 +9147,13 @@
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AK62" t="s" s="2">
+      <c r="AL62" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9167,7 +9164,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9190,16 +9187,16 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="K63" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="K63" t="s" s="2">
+      <c r="L63" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
@@ -9249,7 +9246,7 @@
         <v>77</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>75</v>
@@ -9267,10 +9264,10 @@
         <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9281,11 +9278,11 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9307,16 +9304,16 @@
         <v>179</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>77</v>
@@ -9344,11 +9341,11 @@
         <v>284</v>
       </c>
       <c r="X64" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Y64" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="Y64" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="Z64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9365,7 +9362,7 @@
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>75</v>
@@ -9383,21 +9380,21 @@
         <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9420,13 +9417,13 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>46</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -9477,7 +9474,7 @@
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>75</v>
@@ -9492,24 +9489,24 @@
         <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9535,10 +9532,10 @@
         <v>158</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9589,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>75</v>
@@ -9607,10 +9604,10 @@
         <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9621,7 +9618,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9644,16 +9641,16 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="K67" t="s" s="2">
+      <c r="L67" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
@@ -9703,7 +9700,7 @@
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>75</v>
@@ -9718,13 +9715,13 @@
         <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>127</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
